--- a/scripts/demo/files/groups/재무/급여/2026-10-급여대장.xlsx
+++ b/scripts/demo/files/groups/재무/급여/2026-10-급여대장.xlsx
@@ -444,8 +444,9 @@
       <c r="E2">
         <v>520000</v>
       </c>
-      <c r="F2" t="e">
+      <c r="F2">
         <f>C2+D2-E2</f>
+        <v>3680000</v>
       </c>
     </row>
     <row r="3">
@@ -464,8 +465,9 @@
       <c r="E3">
         <v>480000</v>
       </c>
-      <c r="F3" t="e">
+      <c r="F3">
         <f>C3+D3-E3</f>
+        <v>3420000</v>
       </c>
     </row>
     <row r="4">
@@ -484,8 +486,9 @@
       <c r="E4">
         <v>560000</v>
       </c>
-      <c r="F4" t="e">
+      <c r="F4">
         <f>C4+D4-E4</f>
+        <v>3790000</v>
       </c>
     </row>
     <row r="5">
@@ -504,8 +507,9 @@
       <c r="E5">
         <v>440000</v>
       </c>
-      <c r="F5" t="e">
+      <c r="F5">
         <f>C5+D5-E5</f>
+        <v>3160000</v>
       </c>
     </row>
   </sheetData>
